--- a/src/teste.xlsx
+++ b/src/teste.xlsx
@@ -9,27 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8595"/>
   </bookViews>
   <sheets>
     <sheet name="teste" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="36">
   <si>
     <t xml:space="preserve">troféu </t>
   </si>
   <si>
-    <t>5 de cada</t>
-  </si>
-  <si>
-    <t>2 de cada</t>
-  </si>
-  <si>
     <t>LUGAR</t>
   </si>
   <si>
@@ -48,9 +42,6 @@
     <t>category</t>
   </si>
   <si>
-    <t>quantityForEachClassifiction</t>
-  </si>
-  <si>
     <t>productType</t>
   </si>
   <si>
@@ -109,17 +100,51 @@
   </si>
   <si>
     <t>POSIÇÃO</t>
+  </si>
+  <si>
+    <t>Campeão</t>
+  </si>
+  <si>
+    <t>Vice-Campeão</t>
+  </si>
+  <si>
+    <t>Geral/Pro</t>
+  </si>
+  <si>
+    <t>troféu</t>
+  </si>
+  <si>
+    <t>Geral | Masculino/Feminino | LTDA</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1,5,6,9</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>quantityForEachClassification</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -142,6 +167,12 @@
       <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -216,36 +247,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -253,7 +300,10 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -263,8 +313,27 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" shrinkToFit="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -293,26 +362,7 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" shrinkToFit="0"/>
     </dxf>
     <dxf>
@@ -340,14 +390,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B1:H18">
-  <autoFilter ref="B1:H18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B1:H21">
+  <autoFilter ref="B1:H21"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="productType" dataDxfId="5"/>
-    <tableColumn id="7" name="quantityForEachClassifiction"/>
-    <tableColumn id="2" name="quantity" dataDxfId="4"/>
-    <tableColumn id="3" name="classification" dataDxfId="0"/>
-    <tableColumn id="10" name="nomenclature" dataDxfId="1"/>
+    <tableColumn id="1" name="productType" dataDxfId="1"/>
+    <tableColumn id="7" name="quantityForEachClassification" dataDxfId="0"/>
+    <tableColumn id="2" name="quantity" dataDxfId="6"/>
+    <tableColumn id="3" name="classification" dataDxfId="5"/>
+    <tableColumn id="10" name="nomenclature" dataDxfId="4"/>
     <tableColumn id="4" name="category" dataDxfId="3"/>
     <tableColumn id="5" name="observations" dataDxfId="2"/>
   </tableColumns>
@@ -565,11 +615,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:H19"/>
+  <dimension ref="B1:H29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="2" max="3" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" style="16" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" customWidth="1"/>
     <col min="5" max="5" width="35.7109375" style="10" customWidth="1"/>
     <col min="6" max="6" width="16.42578125" customWidth="1"/>
@@ -579,424 +630,460 @@
   <sheetData>
     <row r="1" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>7</v>
-      </c>
       <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="16">
         <v>2</v>
       </c>
       <c r="D2" s="5">
         <v>10</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>1</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="16">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>6</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="16">
         <v>2</v>
       </c>
       <c r="D4" s="5">
         <v>6</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="16">
         <v>2</v>
       </c>
       <c r="D5" s="5">
         <v>6</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="16">
         <v>2</v>
       </c>
       <c r="D6" s="5">
         <v>6</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="16">
         <v>2</v>
       </c>
       <c r="D7" s="5">
         <v>6</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="16">
         <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>6</v>
       </c>
-      <c r="E8" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>3</v>
-      </c>
+      <c r="E8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="5"/>
       <c r="G8" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="16">
         <v>2</v>
       </c>
       <c r="D9" s="5">
         <v>6</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="16">
         <v>2</v>
       </c>
       <c r="D10" s="5">
         <v>6</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="16">
         <v>2</v>
       </c>
       <c r="D11" s="5">
         <v>6</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="16">
         <v>2</v>
       </c>
       <c r="D12" s="5">
         <v>6</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="16">
         <v>2</v>
       </c>
       <c r="D13" s="5">
         <v>6</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="16">
         <v>2</v>
       </c>
       <c r="D14" s="5">
         <v>3</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="16">
         <v>2</v>
       </c>
       <c r="D15" s="5">
         <v>3</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="16">
         <v>2</v>
       </c>
       <c r="D16" s="5">
         <v>3</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="16">
         <v>2</v>
       </c>
       <c r="D17" s="5">
         <v>3</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>2</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="16">
         <v>2</v>
       </c>
       <c r="D18" s="5">
         <v>10</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="6"/>
+    </row>
+    <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="16">
+        <v>5</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="H18" s="6" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D19" s="5"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="15"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="16">
+        <v>15</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="14"/>
+      <c r="G20" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" s="15"/>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="16">
+        <v>2</v>
+      </c>
+      <c r="D21" s="12"/>
+      <c r="E21" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="G21" s="12"/>
+      <c r="H21" s="15"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G25" s="11"/>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G29" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576 D2:D1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:D1048576">
       <formula1>1</formula1>
       <formula2>1000</formula2>
     </dataValidation>
